--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="M107" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="N107" t="n">
-        <v>3.69</v>
+        <v>3.43</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G123" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,22 +14784,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G139" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G139" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI140"/>
+  <dimension ref="A1:AI139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46094.60416666666</v>
+        <v>46094.625</v>
       </c>
     </row>
     <row r="46">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6449,27 +6449,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46094.625</v>
+        <v>46094.64583333334</v>
       </c>
     </row>
     <row r="52">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>46094.64583333334</v>
+        <v>46094.66666666666</v>
       </c>
     </row>
     <row r="63">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>46094.66666666666</v>
+        <v>46094.67708333334</v>
       </c>
     </row>
     <row r="86">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10843,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>46094.67708333334</v>
+        <v>46094.6875</v>
       </c>
     </row>
     <row r="88">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11566,27 +11566,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="AI94" s="3" t="n">
-        <v>46094.6875</v>
+        <v>46094.69791666666</v>
       </c>
     </row>
     <row r="95">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.02</v>
+        <v>2.09</v>
       </c>
       <c r="M95" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N95" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.53</v>
+        <v>1.72</v>
       </c>
       <c r="M97" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>2.52</v>
+        <v>5</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
       <c r="M106" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N106" t="n">
-        <v>3.43</v>
+        <v>2.16</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="M107" t="n">
-        <v>3.8</v>
+        <v>4.68</v>
       </c>
       <c r="N107" t="n">
-        <v>3.69</v>
+        <v>6.86</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13351,27 +13351,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46094.69791666666</v>
+        <v>46094.70833333334</v>
       </c>
     </row>
     <row r="110">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13708,27 +13708,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46094.70833333334</v>
+        <v>46094.75</v>
       </c>
     </row>
     <row r="113">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46094.75</v>
+        <v>46094.83333333334</v>
       </c>
     </row>
     <row r="114">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46094.83333333334</v>
+        <v>46094.85416666666</v>
       </c>
     </row>
     <row r="115">
@@ -14065,27 +14065,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46094.85416666666</v>
+        <v>46094.875</v>
       </c>
     </row>
     <row r="116">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17031,125 +17031,6 @@
         <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
-        <v>46094.875</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Wellington Phoenix</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Perth Glory FC</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="M140" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N140" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" s="3" t="n">
         <v>46094.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI139"/>
+  <dimension ref="A1:AI144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46094.45833333334</v>
+        <v>46094.46875</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46094.47916666666</v>
+        <v>46094.46875</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46094.48958333334</v>
+        <v>46094.47916666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46094.5</v>
+        <v>46094.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2522,27 +2522,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46094.54166666666</v>
+        <v>46094.5</v>
       </c>
     </row>
     <row r="19">
@@ -2641,27 +2641,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46094.5625</v>
+        <v>46094.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46094.57291666666</v>
+        <v>46094.5625</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46094.58333333334</v>
+        <v>46094.57291666666</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AI42" s="3" t="n">
-        <v>46094.60416666666</v>
+        <v>46094.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46094.60416666666</v>
+        <v>46094.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46094.625</v>
+        <v>46094.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="AI46" s="3" t="n">
-        <v>46094.625</v>
+        <v>46094.60416666666</v>
       </c>
     </row>
     <row r="47">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6449,27 +6449,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="AI51" s="3" t="n">
-        <v>46094.64583333334</v>
+        <v>46094.625</v>
       </c>
     </row>
     <row r="52">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46094.64583333334</v>
+        <v>46094.625</v>
       </c>
     </row>
     <row r="53">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7758,12 +7758,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7868,7 +7868,7 @@
         <v>0</v>
       </c>
       <c r="AI62" s="3" t="n">
-        <v>46094.66666666666</v>
+        <v>46094.64583333334</v>
       </c>
     </row>
     <row r="63">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>46094.66666666666</v>
+        <v>46094.64583333334</v>
       </c>
     </row>
     <row r="64">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="M82" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10605,7 +10605,7 @@
         <v>0</v>
       </c>
       <c r="AI85" s="3" t="n">
-        <v>46094.67708333334</v>
+        <v>46094.66666666666</v>
       </c>
     </row>
     <row r="86">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>46094.67708333334</v>
+        <v>46094.66666666666</v>
       </c>
     </row>
     <row r="87">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10843,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="AI87" s="3" t="n">
-        <v>46094.6875</v>
+        <v>46094.67708333334</v>
       </c>
     </row>
     <row r="88">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>46094.6875</v>
+        <v>46094.67708333334</v>
       </c>
     </row>
     <row r="89">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11566,27 +11566,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11676,7 +11676,7 @@
         <v>0</v>
       </c>
       <c r="AI94" s="3" t="n">
-        <v>46094.69791666666</v>
+        <v>46094.6875</v>
       </c>
     </row>
     <row r="95">
@@ -11685,27 +11685,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="M95" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N95" t="n">
-        <v>3.25</v>
+        <v>4.73</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="AI95" s="3" t="n">
-        <v>46094.69791666666</v>
+        <v>46094.6875</v>
       </c>
     </row>
     <row r="96">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N97" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.02</v>
+        <v>2.53</v>
       </c>
       <c r="M106" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="N106" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46094.70833333334</v>
+        <v>46094.69791666666</v>
       </c>
     </row>
     <row r="110">
@@ -13470,27 +13470,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46094.70833333334</v>
+        <v>46094.69791666666</v>
       </c>
     </row>
     <row r="111">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13708,27 +13708,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13818,7 +13818,7 @@
         <v>0</v>
       </c>
       <c r="AI112" s="3" t="n">
-        <v>46094.75</v>
+        <v>46094.70833333334</v>
       </c>
     </row>
     <row r="113">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46094.83333333334</v>
+        <v>46094.70833333334</v>
       </c>
     </row>
     <row r="114">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46094.85416666666</v>
+        <v>46094.75</v>
       </c>
     </row>
     <row r="115">
@@ -14065,12 +14065,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46094.875</v>
+        <v>46094.75</v>
       </c>
     </row>
     <row r="116">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14294,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="AI116" s="3" t="n">
-        <v>46094.875</v>
+        <v>46094.75</v>
       </c>
     </row>
     <row r="117">
@@ -14303,12 +14303,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="AI117" s="3" t="n">
-        <v>46094.875</v>
+        <v>46094.75</v>
       </c>
     </row>
     <row r="118">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="AI118" s="3" t="n">
-        <v>46094.875</v>
+        <v>46094.75</v>
       </c>
     </row>
     <row r="119">
@@ -14541,27 +14541,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14651,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="AI119" s="3" t="n">
-        <v>46094.875</v>
+        <v>46094.77083333334</v>
       </c>
     </row>
     <row r="120">
@@ -14660,27 +14660,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14770,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="AI120" s="3" t="n">
-        <v>46094.875</v>
+        <v>46094.83333333334</v>
       </c>
     </row>
     <row r="121">
@@ -14779,27 +14779,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="3" t="n">
-        <v>46094.875</v>
+        <v>46094.85416666666</v>
       </c>
     </row>
     <row r="122">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16921,116 +16921,711 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Novi Pazar</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Čukarički</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" s="3" t="n">
+        <v>46094.875</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Železničar Pančevo</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>LFK Mladost Lučani</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" s="3" t="n">
+        <v>46094.875</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Semendrija 1924</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Borac Čačak</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="3" t="n">
+        <v>46094.875</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Radnik Bijeljina</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Sloga Doboj</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" s="3" t="n">
+        <v>46094.875</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Stepojevac Vaga</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>OFK Vršac</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" s="3" t="n">
+        <v>46094.875</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Australia A-League</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Wellington Phoenix</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Perth Glory FC</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L139" t="n">
+      <c r="L144" t="n">
         <v>2.24</v>
       </c>
-      <c r="M139" t="n">
+      <c r="M144" t="n">
         <v>3.81</v>
       </c>
-      <c r="N139" t="n">
+      <c r="N144" t="n">
         <v>3.06</v>
       </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" s="3" t="n">
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" s="3" t="n">
         <v>46094.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.95</v>
+        <v>6.26</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,17 +7081,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,17 +7200,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>6.26</v>
+        <v>3.95</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>3.56</v>
+        <v>4.45</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="M68" t="n">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="N68" t="n">
-        <v>4.23</v>
+        <v>2.26</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.03</v>
+        <v>2.2</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N82" t="n">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="M97" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N97" t="n">
-        <v>5.17</v>
+        <v>3.69</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.53</v>
+        <v>3.02</v>
       </c>
       <c r="M98" t="n">
-        <v>4.68</v>
+        <v>3.28</v>
       </c>
       <c r="N98" t="n">
-        <v>6.86</v>
+        <v>2.16</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.41</v>
+        <v>1.82</v>
       </c>
       <c r="M101" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>3.43</v>
+        <v>3.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="M106" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="N106" t="n">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G143" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>6.26</v>
+        <v>4.34</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>4.34</v>
+        <v>3.95</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N60" t="n">
-        <v>3.44</v>
+        <v>5.95</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="M62" t="n">
         <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>3.86</v>
+        <v>3.44</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.08</v>
+        <v>1.49</v>
       </c>
       <c r="M68" t="n">
-        <v>3.64</v>
+        <v>4.3</v>
       </c>
       <c r="N68" t="n">
-        <v>2.26</v>
+        <v>6.11</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="N80" t="n">
-        <v>2.49</v>
+        <v>4.23</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.95</v>
+        <v>3.02</v>
       </c>
       <c r="M97" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="N97" t="n">
-        <v>3.69</v>
+        <v>2.16</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.02</v>
+        <v>1.72</v>
       </c>
       <c r="M98" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="N98" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12131,7 +12131,7 @@
         <v>1.86</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N101" t="n">
-        <v>3.9</v>
+        <v>5.17</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="M103" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N103" t="n">
-        <v>5.17</v>
+        <v>3.9</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L143" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.04</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>4.28</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.56</v>
+        <v>4.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7081,17 +7081,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>6.26</v>
+        <v>3.44</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>3.86</v>
+        <v>4.34</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M60" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>5.95</v>
+        <v>6.26</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>3.44</v>
+        <v>3.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="M68" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>6.11</v>
+        <v>2.65</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.55</v>
+        <v>1.49</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N70" t="n">
-        <v>2.65</v>
+        <v>6.11</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M90" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N90" t="n">
-        <v>4.73</v>
+        <v>2.46</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="M98" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="M99" t="n">
-        <v>4.68</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>6.86</v>
+        <v>3.9</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="M104" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="N104" t="n">
-        <v>2.52</v>
+        <v>3.43</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="M105" t="n">
-        <v>3.2</v>
+        <v>4.68</v>
       </c>
       <c r="N105" t="n">
-        <v>3.25</v>
+        <v>6.86</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="M109" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N109" t="n">
-        <v>3.43</v>
+        <v>5.17</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -17164,22 +17164,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,22 +17283,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L143" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="M56" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N56" t="n">
-        <v>5.95</v>
+        <v>3.95</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>3.56</v>
+        <v>3.21</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>3.44</v>
+        <v>6.26</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>4.34</v>
+        <v>3.44</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N60" t="n">
-        <v>6.26</v>
+        <v>5.95</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>3.95</v>
+        <v>4.34</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.02</v>
+        <v>2.09</v>
       </c>
       <c r="M97" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N97" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.53</v>
+        <v>1.53</v>
       </c>
       <c r="M100" t="n">
-        <v>3.14</v>
+        <v>4.68</v>
       </c>
       <c r="N100" t="n">
-        <v>2.52</v>
+        <v>6.86</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="M102" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N102" t="n">
-        <v>3.69</v>
+        <v>4.3</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="M107" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="M108" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N108" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.51</v>
+        <v>3.02</v>
       </c>
       <c r="M109" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="N109" t="n">
-        <v>5.17</v>
+        <v>2.16</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.79</v>
+        <v>2.47</v>
       </c>
       <c r="M134" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="N134" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G143" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.56</v>
+        <v>4.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="M57" t="n">
         <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>3.21</v>
+        <v>4.34</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>6.26</v>
+        <v>3.86</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="M60" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>5.95</v>
+        <v>3.95</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>4.45</v>
+        <v>6.26</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="M62" t="n">
         <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>4.34</v>
+        <v>3.21</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="M63" t="n">
         <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>3.86</v>
+        <v>3.44</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N80" t="n">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N92" t="n">
-        <v>4.73</v>
+        <v>2.46</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="M100" t="n">
-        <v>4.68</v>
+        <v>3.5</v>
       </c>
       <c r="N100" t="n">
-        <v>6.86</v>
+        <v>5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.53</v>
+        <v>3.02</v>
       </c>
       <c r="M101" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="N101" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="M102" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N102" t="n">
-        <v>4.3</v>
+        <v>3.69</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="M107" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="N107" t="n">
-        <v>3.69</v>
+        <v>3.43</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.72</v>
+        <v>2.53</v>
       </c>
       <c r="M108" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N108" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.02</v>
+        <v>2.09</v>
       </c>
       <c r="M109" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N109" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,17 +15173,17 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G143" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>3.56</v>
+        <v>6.26</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>4.34</v>
+        <v>3.56</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N58" t="n">
-        <v>3.86</v>
+        <v>3.21</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.95</v>
+        <v>4.34</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>6.26</v>
+        <v>3.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N62" t="n">
-        <v>3.21</v>
+        <v>5.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.08</v>
+        <v>1.49</v>
       </c>
       <c r="M80" t="n">
-        <v>3.64</v>
+        <v>4.3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.26</v>
+        <v>6.11</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="M98" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N98" t="n">
-        <v>4.3</v>
+        <v>4.93</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="M99" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="M101" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="N101" t="n">
-        <v>2.16</v>
+        <v>3.69</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="M102" t="n">
-        <v>3.8</v>
+        <v>4.68</v>
       </c>
       <c r="N102" t="n">
-        <v>3.69</v>
+        <v>6.86</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="M104" t="n">
-        <v>4.68</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>6.86</v>
+        <v>3.22</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="M105" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N105" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,22 +16688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,22 +17045,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G143" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI144"/>
+  <dimension ref="A1:AI140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>5.04</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>4.28</v>
       </c>
       <c r="N39" t="n">
-        <v>3.63</v>
+        <v>1.53</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.86</v>
+        <v>3.21</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>6.26</v>
+        <v>4.34</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>3.21</v>
+        <v>6.26</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
         <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>4.34</v>
+        <v>3.86</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="M62" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>5.95</v>
+        <v>3.44</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.03</v>
+        <v>1.89</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="N64" t="n">
-        <v>2.18</v>
+        <v>4.23</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="M75" t="n">
-        <v>3.64</v>
+        <v>3.15</v>
       </c>
       <c r="N75" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="M78" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>4.23</v>
+        <v>3.45</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.2</v>
+        <v>3.03</v>
       </c>
       <c r="M82" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>3.45</v>
+        <v>2.18</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.51</v>
+        <v>2.53</v>
       </c>
       <c r="M97" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="N97" t="n">
-        <v>5.17</v>
+        <v>2.52</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="M98" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>4.93</v>
+        <v>3.25</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.72</v>
+        <v>3.02</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12250,7 +12250,7 @@
         <v>1.86</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M101" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>3.69</v>
+        <v>3.22</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="M103" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="N103" t="n">
-        <v>3.43</v>
+        <v>3.69</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="M105" t="n">
-        <v>3.65</v>
+        <v>3.23</v>
       </c>
       <c r="N105" t="n">
-        <v>4.3</v>
+        <v>3.43</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.53</v>
+        <v>1.51</v>
       </c>
       <c r="M108" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="N108" t="n">
-        <v>2.52</v>
+        <v>5.17</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="M109" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N109" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.02</v>
+        <v>1.53</v>
       </c>
       <c r="M110" t="n">
-        <v>3.28</v>
+        <v>4.68</v>
       </c>
       <c r="N110" t="n">
-        <v>2.16</v>
+        <v>6.86</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.47</v>
+        <v>1.79</v>
       </c>
       <c r="M137" t="n">
-        <v>2.62</v>
+        <v>3.45</v>
       </c>
       <c r="N137" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17040,27 +17040,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17150,482 +17150,6 @@
         <v>0</v>
       </c>
       <c r="AI140" s="3" t="n">
-        <v>46094.875</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>OFK Beograd</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="V141" t="n">
-        <v>0</v>
-      </c>
-      <c r="W141" t="n">
-        <v>0</v>
-      </c>
-      <c r="X141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI141" s="3" t="n">
-        <v>46094.875</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Železničar Pančevo</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>LFK Mladost Lučani</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" t="n">
-        <v>0</v>
-      </c>
-      <c r="W142" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI142" s="3" t="n">
-        <v>46094.875</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Dinamo Jug</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" t="n">
-        <v>0</v>
-      </c>
-      <c r="W143" t="n">
-        <v>0</v>
-      </c>
-      <c r="X143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI143" s="3" t="n">
-        <v>46094.875</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Wellington Phoenix</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Perth Glory FC</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L144" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="M144" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N144" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI144" s="3" t="n">
         <v>46094.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,17 +7319,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>3.56</v>
+        <v>4.34</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>4.45</v>
+        <v>6.26</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N62" t="n">
-        <v>3.44</v>
+        <v>5.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="M63" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>5.95</v>
+        <v>3.44</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="M64" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N64" t="n">
-        <v>4.23</v>
+        <v>2.65</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.49</v>
+        <v>3.08</v>
       </c>
       <c r="M72" t="n">
-        <v>4.3</v>
+        <v>3.64</v>
       </c>
       <c r="N72" t="n">
-        <v>6.11</v>
+        <v>2.26</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="M97" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="N97" t="n">
-        <v>2.52</v>
+        <v>3.43</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="M98" t="n">
-        <v>3.2</v>
+        <v>4.68</v>
       </c>
       <c r="N98" t="n">
-        <v>3.25</v>
+        <v>6.86</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.02</v>
+        <v>1.51</v>
       </c>
       <c r="M99" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="N99" t="n">
-        <v>2.16</v>
+        <v>5.17</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="M103" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N103" t="n">
-        <v>3.69</v>
+        <v>4.93</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,55 +13035,55 @@
         </is>
       </c>
       <c r="L106" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M106" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N106" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB106" t="n">
         <v>1.82</v>
-      </c>
-      <c r="M106" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N106" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="M108" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N108" t="n">
-        <v>5.17</v>
+        <v>3.22</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="M109" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N109" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="M110" t="n">
-        <v>4.68</v>
+        <v>3.65</v>
       </c>
       <c r="N110" t="n">
-        <v>6.86</v>
+        <v>4.3</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16688,22 +16688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G139" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4.45</v>
+        <v>3.44</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M57" t="n">
         <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.56</v>
+        <v>3.86</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7319,17 +7319,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="M59" t="n">
         <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>4.34</v>
+        <v>3.21</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.95</v>
+        <v>6.26</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N61" t="n">
-        <v>6.26</v>
+        <v>5.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="M62" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>5.95</v>
+        <v>4.34</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>3.44</v>
+        <v>4.45</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="M71" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>4.23</v>
+        <v>3.45</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N89" t="n">
-        <v>2.46</v>
+        <v>4.73</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="M97" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="N97" t="n">
-        <v>3.43</v>
+        <v>3.69</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="M100" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N100" t="n">
-        <v>3.69</v>
+        <v>4.3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>5</v>
+        <v>3.22</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.82</v>
+        <v>2.53</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N102" t="n">
-        <v>3.9</v>
+        <v>2.52</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.53</v>
+        <v>1.82</v>
       </c>
       <c r="M104" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="N104" t="n">
-        <v>2.52</v>
+        <v>3.9</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.15</v>
+        <v>3.02</v>
       </c>
       <c r="M108" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N108" t="n">
-        <v>3.22</v>
+        <v>2.16</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="M110" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N110" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16006,7 +16006,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.44</v>
+        <v>4.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>3.56</v>
+        <v>6.26</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>3.86</v>
+        <v>3.21</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>6.26</v>
+        <v>3.44</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="M61" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>5.95</v>
+        <v>3.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,22 +7763,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="M63" t="n">
         <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>4.45</v>
+        <v>4.34</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.03</v>
+        <v>1.49</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N76" t="n">
-        <v>2.18</v>
+        <v>6.11</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="M97" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>3.69</v>
+        <v>4.93</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="M99" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.53</v>
+        <v>3.02</v>
       </c>
       <c r="M102" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="N102" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.75</v>
+        <v>2.53</v>
       </c>
       <c r="M103" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N103" t="n">
-        <v>4.93</v>
+        <v>2.52</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="M104" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N104" t="n">
-        <v>3.9</v>
+        <v>5.17</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="M105" t="n">
-        <v>4.68</v>
+        <v>3.8</v>
       </c>
       <c r="N105" t="n">
-        <v>6.86</v>
+        <v>3.69</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="M107" t="n">
-        <v>3.2</v>
+        <v>4.68</v>
       </c>
       <c r="N107" t="n">
-        <v>3.25</v>
+        <v>6.86</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.02</v>
+        <v>2.09</v>
       </c>
       <c r="M108" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N108" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="M110" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N110" t="n">
-        <v>5</v>
+        <v>3.43</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,22 +15974,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N57" t="n">
-        <v>3.21</v>
+        <v>3.95</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N58" t="n">
-        <v>3.95</v>
+        <v>3.21</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>3.56</v>
+        <v>4.34</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M60" t="n">
         <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="M61" t="n">
         <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>3.86</v>
+        <v>3.44</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,22 +7763,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G139" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>6.26</v>
+        <v>3.44</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="M57" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="M61" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>3.44</v>
+        <v>6.26</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="M62" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>3.86</v>
+        <v>3.21</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="M75" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="N75" t="n">
-        <v>2.49</v>
+        <v>4.23</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="N79" t="n">
-        <v>3.45</v>
+        <v>6.11</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.08</v>
+        <v>2.2</v>
       </c>
       <c r="M83" t="n">
-        <v>3.64</v>
+        <v>3.1</v>
       </c>
       <c r="N83" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N91" t="n">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="M97" t="n">
         <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>4.93</v>
+        <v>3.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="M98" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N98" t="n">
-        <v>4.3</v>
+        <v>5.17</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N100" t="n">
-        <v>3.22</v>
+        <v>3.69</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.02</v>
+        <v>2.41</v>
       </c>
       <c r="M102" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="N102" t="n">
-        <v>2.16</v>
+        <v>3.43</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.53</v>
+        <v>1.72</v>
       </c>
       <c r="M103" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="N103" t="n">
-        <v>2.52</v>
+        <v>5</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.51</v>
+        <v>2.15</v>
       </c>
       <c r="M104" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>5.17</v>
+        <v>3.22</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="M106" t="n">
-        <v>3.5</v>
+        <v>4.68</v>
       </c>
       <c r="N106" t="n">
-        <v>3.9</v>
+        <v>6.86</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.53</v>
+        <v>3.02</v>
       </c>
       <c r="M107" t="n">
-        <v>4.68</v>
+        <v>3.28</v>
       </c>
       <c r="N107" t="n">
-        <v>6.86</v>
+        <v>2.16</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.09</v>
+        <v>2.53</v>
       </c>
       <c r="M108" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="N108" t="n">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.41</v>
+        <v>2.09</v>
       </c>
       <c r="M110" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N110" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,22 +15974,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G139" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5827,10 +5827,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="M53" t="n">
         <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>4.45</v>
+        <v>3.21</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,17 +7200,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
         <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>3.56</v>
+        <v>3.86</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>4.34</v>
+        <v>3.56</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N60" t="n">
-        <v>3.95</v>
+        <v>3.44</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>6.26</v>
+        <v>3.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>3.21</v>
+        <v>6.26</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="M63" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>5.95</v>
+        <v>4.34</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="M95" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N95" t="n">
-        <v>2.46</v>
+        <v>4.73</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N96" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.95</v>
+        <v>3.02</v>
       </c>
       <c r="M100" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="N100" t="n">
-        <v>3.69</v>
+        <v>2.16</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N101" t="n">
-        <v>4.93</v>
+        <v>3.25</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.72</v>
+        <v>2.53</v>
       </c>
       <c r="M103" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="N103" t="n">
-        <v>5</v>
+        <v>2.52</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N104" t="n">
-        <v>3.22</v>
+        <v>3.69</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M106" t="n">
-        <v>4.68</v>
+        <v>4.1</v>
       </c>
       <c r="N106" t="n">
-        <v>6.86</v>
+        <v>5.17</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="M107" t="n">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="N107" t="n">
-        <v>2.16</v>
+        <v>4.3</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.53</v>
+        <v>1.53</v>
       </c>
       <c r="M108" t="n">
-        <v>3.14</v>
+        <v>4.68</v>
       </c>
       <c r="N108" t="n">
-        <v>2.52</v>
+        <v>6.86</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,17 +15173,17 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15974,22 +15974,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,22 +16212,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16363,17 +16363,17 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,22 +16926,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G139" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
         <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.21</v>
+        <v>4.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="M54" t="n">
         <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>4.45</v>
+        <v>3.21</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="M95" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N95" t="n">
-        <v>4.73</v>
+        <v>2.46</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="M96" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>5</v>
+        <v>3.22</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="M97" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="M99" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>3.43</v>
+        <v>4.93</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.02</v>
+        <v>2.41</v>
       </c>
       <c r="M100" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="N100" t="n">
-        <v>2.16</v>
+        <v>3.43</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.09</v>
+        <v>1.82</v>
       </c>
       <c r="M101" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="M104" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N104" t="n">
-        <v>3.69</v>
+        <v>5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="M105" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N105" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.67</v>
+        <v>2.53</v>
       </c>
       <c r="M107" t="n">
-        <v>3.65</v>
+        <v>3.14</v>
       </c>
       <c r="N107" t="n">
-        <v>4.3</v>
+        <v>2.52</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="M108" t="n">
-        <v>4.68</v>
+        <v>3.8</v>
       </c>
       <c r="N108" t="n">
-        <v>6.86</v>
+        <v>3.69</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.75</v>
+        <v>3.02</v>
       </c>
       <c r="M109" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N109" t="n">
-        <v>4.93</v>
+        <v>2.16</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,22 +15141,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15498,22 +15498,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,22 +15974,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G138" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N96" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="M104" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N104" t="n">
-        <v>5</v>
+        <v>3.22</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI140"/>
+  <dimension ref="A1:AI139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.26</v>
+        <v>2.07</v>
       </c>
       <c r="M44" t="n">
-        <v>4.05</v>
+        <v>2.85</v>
       </c>
       <c r="N44" t="n">
-        <v>1.71</v>
+        <v>4.13</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.33</v>
+        <v>4.26</v>
       </c>
       <c r="M45" t="n">
-        <v>3.74</v>
+        <v>4.05</v>
       </c>
       <c r="N45" t="n">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5827,10 +5827,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="M46" t="n">
-        <v>2.85</v>
+        <v>3.74</v>
       </c>
       <c r="N46" t="n">
-        <v>4.13</v>
+        <v>2.66</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5946,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="M53" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4.45</v>
+        <v>3.86</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>3.21</v>
+        <v>3.44</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
         <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>3.86</v>
+        <v>3.56</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>3.56</v>
+        <v>4.45</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="M60" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N60" t="n">
-        <v>3.44</v>
+        <v>5.95</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>3.95</v>
+        <v>6.26</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>6.26</v>
+        <v>4.34</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>4.34</v>
+        <v>3.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.03</v>
+        <v>1.89</v>
       </c>
       <c r="M71" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="N71" t="n">
-        <v>2.18</v>
+        <v>4.23</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N87" t="n">
-        <v>2.87</v>
+        <v>3.62</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M88" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N88" t="n">
-        <v>3.62</v>
+        <v>2.87</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="M93" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="N93" t="n">
-        <v>4.8</v>
+        <v>5.48</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.48</v>
+        <v>2.65</v>
       </c>
       <c r="M94" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>5.48</v>
+        <v>2.46</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="M95" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N95" t="n">
-        <v>2.46</v>
+        <v>4.73</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="N97" t="n">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>4.93</v>
+        <v>4.3</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="M104" t="n">
-        <v>3.3</v>
+        <v>4.68</v>
       </c>
       <c r="N104" t="n">
-        <v>3.22</v>
+        <v>6.86</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.09</v>
+        <v>2.41</v>
       </c>
       <c r="M105" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="N105" t="n">
-        <v>3.25</v>
+        <v>3.43</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="M110" t="n">
-        <v>4.68</v>
+        <v>3.2</v>
       </c>
       <c r="N110" t="n">
-        <v>6.86</v>
+        <v>3.25</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16363,7 +16363,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17031,125 +17031,6 @@
         <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
-        <v>46094.875</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Wellington Phoenix</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Perth Glory FC</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L140" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="M140" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N140" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" s="3" t="n">
         <v>46094.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="M53" t="n">
         <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>3.86</v>
+        <v>3.44</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N54" t="n">
-        <v>3.44</v>
+        <v>4.34</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6962,17 +6962,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N59" t="n">
-        <v>4.45</v>
+        <v>5.95</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="M60" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>5.95</v>
+        <v>6.26</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>6.26</v>
+        <v>3.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="M62" t="n">
         <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>4.34</v>
+        <v>4.45</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7914,17 +7914,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M70" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="N70" t="n">
-        <v>5.53</v>
+        <v>6.11</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="N73" t="n">
-        <v>2.49</v>
+        <v>4.23</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M87" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>3.62</v>
+        <v>2.87</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="M88" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N88" t="n">
-        <v>2.87</v>
+        <v>3.62</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.02</v>
+        <v>1.75</v>
       </c>
       <c r="M97" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>2.16</v>
+        <v>4.93</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.75</v>
+        <v>3.02</v>
       </c>
       <c r="M98" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N98" t="n">
-        <v>4.93</v>
+        <v>2.16</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N101" t="n">
-        <v>3.22</v>
+        <v>3.69</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="M102" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>5.17</v>
+        <v>3.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.53</v>
+        <v>2.53</v>
       </c>
       <c r="M104" t="n">
-        <v>4.68</v>
+        <v>3.14</v>
       </c>
       <c r="N104" t="n">
-        <v>6.86</v>
+        <v>2.52</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.41</v>
+        <v>1.51</v>
       </c>
       <c r="M105" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N105" t="n">
-        <v>3.43</v>
+        <v>5.17</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.53</v>
+        <v>1.67</v>
       </c>
       <c r="M106" t="n">
-        <v>3.14</v>
+        <v>3.65</v>
       </c>
       <c r="N106" t="n">
-        <v>2.52</v>
+        <v>4.3</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="M108" t="n">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="N108" t="n">
-        <v>3.69</v>
+        <v>3.43</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="M110" t="n">
-        <v>3.2</v>
+        <v>4.68</v>
       </c>
       <c r="N110" t="n">
-        <v>3.25</v>
+        <v>6.86</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,22 +15022,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15054,17 +15054,17 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G138" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI139"/>
+  <dimension ref="A1:AI138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.26</v>
+        <v>2.33</v>
       </c>
       <c r="M45" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="N45" t="n">
-        <v>1.71</v>
+        <v>2.66</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5827,10 +5827,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.33</v>
+        <v>4.26</v>
       </c>
       <c r="M46" t="n">
-        <v>3.74</v>
+        <v>4.05</v>
       </c>
       <c r="N46" t="n">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5946,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="M48" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AI52" s="3" t="n">
-        <v>46094.625</v>
+        <v>46094.64583333334</v>
       </c>
     </row>
     <row r="53">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.44</v>
+        <v>4.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N55" t="n">
-        <v>3.21</v>
+        <v>3.44</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="M59" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N59" t="n">
-        <v>5.95</v>
+        <v>4.34</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>6.26</v>
+        <v>3.95</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,55 +7680,55 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N61" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
         <v>1.92</v>
       </c>
-      <c r="M61" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N61" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>4.45</v>
+        <v>6.26</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7877,12 +7877,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7914,17 +7914,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7987,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
-        <v>46094.64583333334</v>
+        <v>46094.66666666666</v>
       </c>
     </row>
     <row r="64">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.03</v>
+        <v>2.6</v>
       </c>
       <c r="M75" t="n">
         <v>3.4</v>
       </c>
       <c r="N75" t="n">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.08</v>
+        <v>1.89</v>
       </c>
       <c r="M78" t="n">
-        <v>3.64</v>
+        <v>3.32</v>
       </c>
       <c r="N78" t="n">
-        <v>2.26</v>
+        <v>4.23</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="AI86" s="3" t="n">
-        <v>46094.66666666666</v>
+        <v>46094.67708333334</v>
       </c>
     </row>
     <row r="87">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N87" t="n">
-        <v>2.87</v>
+        <v>3.62</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10852,12 +10852,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="M88" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="N88" t="n">
-        <v>3.62</v>
+        <v>5.48</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
       <c r="AI88" s="3" t="n">
-        <v>46094.67708333334</v>
+        <v>46094.6875</v>
       </c>
     </row>
     <row r="89">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.48</v>
+        <v>2.65</v>
       </c>
       <c r="M93" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>5.48</v>
+        <v>2.46</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N94" t="n">
-        <v>2.46</v>
+        <v>4.73</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11685,27 +11685,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="M95" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N95" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>0</v>
       </c>
       <c r="AI95" s="3" t="n">
-        <v>46094.6875</v>
+        <v>46094.69791666666</v>
       </c>
     </row>
     <row r="96">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.02</v>
+        <v>2.15</v>
       </c>
       <c r="M98" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N98" t="n">
-        <v>2.16</v>
+        <v>3.22</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N100" t="n">
-        <v>3.22</v>
+        <v>3.43</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="M101" t="n">
-        <v>3.8</v>
+        <v>4.68</v>
       </c>
       <c r="N101" t="n">
-        <v>3.69</v>
+        <v>6.86</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.82</v>
+        <v>2.09</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N102" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.53</v>
+        <v>1.75</v>
       </c>
       <c r="M104" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="N104" t="n">
-        <v>2.52</v>
+        <v>4.93</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="M105" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N105" t="n">
-        <v>5.17</v>
+        <v>3.69</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="M106" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N106" t="n">
-        <v>4.3</v>
+        <v>5.17</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,22 +13237,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.41</v>
+        <v>3.02</v>
       </c>
       <c r="M108" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N108" t="n">
-        <v>3.43</v>
+        <v>2.16</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="M110" t="n">
-        <v>4.68</v>
+        <v>3.48</v>
       </c>
       <c r="N110" t="n">
-        <v>6.86</v>
+        <v>3.07</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46094.69791666666</v>
+        <v>46094.70833333334</v>
       </c>
     </row>
     <row r="111">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46094.70833333334</v>
+        <v>46094.75</v>
       </c>
     </row>
     <row r="114">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14422,27 +14422,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14532,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="AI118" s="3" t="n">
-        <v>46094.75</v>
+        <v>46094.77083333334</v>
       </c>
     </row>
     <row r="119">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14651,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="AI119" s="3" t="n">
-        <v>46094.77083333334</v>
+        <v>46094.83333333334</v>
       </c>
     </row>
     <row r="120">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14770,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="AI120" s="3" t="n">
-        <v>46094.83333333334</v>
+        <v>46094.85416666666</v>
       </c>
     </row>
     <row r="121">
@@ -14779,27 +14779,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="3" t="n">
-        <v>46094.85416666666</v>
+        <v>46094.875</v>
       </c>
     </row>
     <row r="122">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,22 +16569,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Perth Glory FC</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16912,125 +16912,6 @@
         <v>0</v>
       </c>
       <c r="AI138" s="3" t="n">
-        <v>46094.875</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Wellington Phoenix</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Perth Glory FC</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L139" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="M139" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N139" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="V139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
-        <v>0</v>
-      </c>
-      <c r="X139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" s="3" t="n">
         <v>46094.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.07</v>
+        <v>4.26</v>
       </c>
       <c r="M44" t="n">
-        <v>2.85</v>
+        <v>4.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4.13</v>
+        <v>1.71</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5708,10 +5708,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="M45" t="n">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="N45" t="n">
-        <v>2.66</v>
+        <v>4.13</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5827,10 +5827,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.26</v>
+        <v>2.33</v>
       </c>
       <c r="M46" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="N46" t="n">
-        <v>1.71</v>
+        <v>2.66</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5946,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.1</v>
+        <v>2.64</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>2.69</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>3.21</v>
+        <v>3.56</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="M53" t="n">
         <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>4.45</v>
+        <v>4.34</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.07</v>
+        <v>1.47</v>
       </c>
       <c r="M55" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>3.44</v>
+        <v>6.26</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
         <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>3.56</v>
+        <v>3.86</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="M59" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>4.34</v>
+        <v>3.44</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,17 +7557,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>6.26</v>
+        <v>3.21</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.03</v>
+        <v>1.89</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="N63" t="n">
-        <v>2.18</v>
+        <v>4.23</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.08</v>
+        <v>1.44</v>
       </c>
       <c r="M76" t="n">
-        <v>3.64</v>
+        <v>4.45</v>
       </c>
       <c r="N76" t="n">
-        <v>2.26</v>
+        <v>5.53</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="M88" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>5.48</v>
+        <v>3.44</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="M92" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N92" t="n">
-        <v>3.44</v>
+        <v>2.46</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N93" t="n">
-        <v>2.46</v>
+        <v>4.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="M95" t="n">
-        <v>3.5</v>
+        <v>4.68</v>
       </c>
       <c r="N95" t="n">
-        <v>5</v>
+        <v>6.86</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="N96" t="n">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="M98" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N98" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.41</v>
+        <v>1.82</v>
       </c>
       <c r="M100" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="N100" t="n">
-        <v>3.43</v>
+        <v>3.9</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M101" t="n">
-        <v>4.68</v>
+        <v>4.1</v>
       </c>
       <c r="N101" t="n">
-        <v>6.86</v>
+        <v>5.17</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="M102" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N102" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.53</v>
+        <v>1.75</v>
       </c>
       <c r="M103" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="N103" t="n">
-        <v>2.52</v>
+        <v>4.93</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.82</v>
+        <v>2.41</v>
       </c>
       <c r="M107" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N107" t="n">
-        <v>3.9</v>
+        <v>3.43</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.02</v>
+        <v>1.72</v>
       </c>
       <c r="M108" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="N108" t="n">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13321,7 +13321,7 @@
         <v>1.86</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,22 +13356,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,22 +13713,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14784,22 +14784,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,22 +15617,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,22 +15736,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,22 +16093,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,22 +16331,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16363,7 +16363,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G137" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.24</v>
+        <v>2.84</v>
       </c>
       <c r="R8" t="n">
-        <v>2.22</v>
+        <v>3.05</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2977,70 +2977,70 @@
         <v>2.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7902,124 +7902,124 @@
         <v>2.6</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -9084,124 +9084,124 @@
         <v>4.13</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>3.44</v>
+        <v>3.21</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>3.21</v>
+        <v>3.44</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,22 +26363,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-03-13.xlsx
+++ b/jogos_2026-03-13.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="R21" t="n">
-        <v>3.46</v>
+        <v>3.76</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4750,40 +4750,40 @@
         <v>5.29</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
         <v>1.81</v>
@@ -4792,82 +4792,82 @@
         <v>1.94</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6326,70 +6326,70 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.13</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.24</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>3.12</v>
+        <v>1.32</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.26</v>
+        <v>3.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="R45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W45" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX45" t="n">
         <v>1.71</v>
       </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="R46" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R47" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.64</v>
+        <v>2.41</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="R48" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,79 +10060,79 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10174,19 +10174,19 @@
         <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q52" t="n">
         <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>3.56</v>
+        <v>3.86</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,79 +11636,79 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>3.95</v>
+        <v>3.21</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -11750,19 +11750,19 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R58" t="n">
-        <v>4.34</v>
+        <v>3.44</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>3.44</v>
+        <v>4.34</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13024,124 +13024,124 @@
         <v>6.11</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AO64" t="n">
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS64" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW64" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX64" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA64" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC64" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD64" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF64" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,133 +13409,133 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="R66" t="n">
-        <v>4.23</v>
+        <v>2.65</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL66" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AM66" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN66" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR66" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AU66" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AV66" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB66" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD66" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE66" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BF66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,79 +13606,79 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
@@ -13687,52 +13687,52 @@
         <v>0</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR67" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU67" t="n">
         <v>0</v>
       </c>
       <c r="AV67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW67" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX67" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BD67" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE67" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF67" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,133 +13803,133 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
       <c r="AU68" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV68" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AW68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY68" t="n">
         <v>0</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA68" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB68" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BD68" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF68" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,133 +14000,133 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI69" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK69" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL69" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM69" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN69" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO69" t="n">
         <v>0</v>
       </c>
       <c r="AP69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS69" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU69" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW69" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX69" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY69" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ69" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA69" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB69" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC69" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD69" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE69" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,133 +14197,133 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI70" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL70" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AM70" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AO70" t="n">
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR70" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV70" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY70" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BA70" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB70" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD70" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE70" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF70" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,133 +14394,133 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM71" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN71" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO71" t="n">
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS71" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU71" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV71" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX71" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA71" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BB71" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD71" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE71" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF71" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,133 +15182,133 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AM75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AN75" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO75" t="n">
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR75" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS75" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY75" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA75" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BB75" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC75" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD75" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE75" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BF75" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,133 +15379,133 @@
         </is>
       </c>
       <c r="P76" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W76" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X76" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK76" t="n">
         <v>1.44</v>
       </c>
-      <c r="Q76" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="R76" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>0</v>
-      </c>
       <c r="AL76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM76" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
       </c>
       <c r="AP76" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR76" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS76" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU76" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW76" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA76" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BB76" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC76" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE76" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF76" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,79 +15576,79 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL77" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AM77" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO77" t="n">
         <v>0</v>
@@ -15657,52 +15657,52 @@
         <v>0</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR77" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS77" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU77" t="n">
         <v>0</v>
       </c>
       <c r="AV77" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AW77" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AX77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AY77" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ77" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BA77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB77" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC77" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD77" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE77" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BF77" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,133 +15773,133 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL78" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AM78" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN78" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO78" t="n">
         <v>0</v>
       </c>
       <c r="AP78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR78" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX78" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AY78" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BB78" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD78" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="BE78" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF78" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,133 +15970,133 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q79" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W79" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="X79" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV79" t="n">
         <v>3.15</v>
       </c>
-      <c r="R79" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV79" t="n">
-        <v>0</v>
-      </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX79" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB79" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC79" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD79" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE79" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF79" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,133 +16167,133 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16364,133 +16364,133 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.08</v>
+        <v>2.84</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="R81" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S81" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T81" t="n">
         <v>2.26</v>
       </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL81" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AM81" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS81" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BB81" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC81" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD81" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF81" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,133 +16561,133 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R82" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL82" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM82" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN82" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR82" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AX82" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF82" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,133 +17152,133 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK85" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL85" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AM85" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN85" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO85" t="n">
         <v>0</v>
       </c>
       <c r="AP85" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR85" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU85" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV85" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW85" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY85" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ85" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA85" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB85" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC85" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD85" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="BE85" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF85" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG85" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,79 +17940,79 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI89" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK89" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM89" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN89" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AO89" t="n">
         <v>0</v>
@@ -18054,19 +18054,19 @@
         <v>0</v>
       </c>
       <c r="BB89" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC89" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD89" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE89" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF89" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R91" t="n">
-        <v>5.48</v>
+        <v>4.73</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R92" t="n">
-        <v>2.46</v>
+        <v>4.8</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R93" t="n">
-        <v>4.8</v>
+        <v>2.46</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.53</v>
+        <v>2.09</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.68</v>
+        <v>3.2</v>
       </c>
       <c r="R95" t="n">
-        <v>6.86</v>
+        <v>3.25</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.02</v>
+        <v>2.53</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="R96" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="R97" t="n">
-        <v>3.22</v>
+        <v>8</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R98" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.53</v>
+        <v>1.67</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.14</v>
+        <v>3.65</v>
       </c>
       <c r="R99" t="n">
-        <v>2.52</v>
+        <v>4.3</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="R101" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="R102" t="n">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q103" t="n">
         <v>3.5</v>
       </c>
       <c r="R103" t="n">
-        <v>4.93</v>
+        <v>3.9</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="R104" t="n">
-        <v>3.05</v>
+        <v>3.43</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R105" t="n">
-        <v>3.69</v>
+        <v>4.93</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.33</v>
+        <v>2.33</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="R106" t="n">
-        <v>8</v>
+        <v>3.05</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.41</v>
+        <v>1.53</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.23</v>
+        <v>4.68</v>
       </c>
       <c r="R107" t="n">
-        <v>3.43</v>
+        <v>6.86</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="R108" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="R112" t="n">
-        <v>1.73</v>
+        <v>3.07</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF133" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
